--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487719_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487719_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8059</v>
+        <v>1.9333</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8355</v>
+        <v>1.9356</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0296</v>
+        <v>-0.0023</v>
       </c>
       <c r="G2" t="n">
         <v>-0.058</v>
@@ -610,13 +610,13 @@
         <v>0.7761</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4181</v>
+        <v>-0.2908</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3028</v>
+        <v>-0.2027</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.506</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.0461</v>
+        <v>-0.6858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.7264</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7119</v>
+        <v>-1.4121</v>
       </c>
       <c r="G3" t="n">
         <v>-2.2665</v>
@@ -688,13 +688,13 @@
         <v>0.5821</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1214</v>
+        <v>-0.761</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7874</v>
+        <v>-0.7268</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.334</v>
+        <v>-0.0342</v>
       </c>
       <c r="V3" t="n">
         <v>2.7298</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.2387</v>
+        <v>-0.7507</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6533</v>
+        <v>4.1959</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.8921</v>
+        <v>-4.9466</v>
       </c>
       <c r="G4" t="n">
         <v>1.1033</v>
@@ -766,13 +766,13 @@
         <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8196</v>
+        <v>-1.3316</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0902</v>
+        <v>-0.5476</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7294</v>
+        <v>-0.7839</v>
       </c>
       <c r="V4" t="n">
         <v>1.2239</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2843</v>
+        <v>-1.3995</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0171</v>
+        <v>2.0381</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.3014</v>
+        <v>-3.4377</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7073</v>
@@ -844,13 +844,13 @@
         <v>0.5821</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2366</v>
+        <v>-0.3519</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1828</v>
+        <v>0.2038</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4194</v>
+        <v>-0.5557</v>
       </c>
       <c r="V5" t="n">
         <v>0.0478</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1317</v>
+        <v>-1.9498</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1314</v>
+        <v>-0.0313</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0002</v>
+        <v>-1.9185</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0192</v>
@@ -922,13 +922,13 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0244</v>
+        <v>-0.8426</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8479</v>
+        <v>-0.7478</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1765</v>
+        <v>-0.0948</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GIRALDO SISTIAGA</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3662</v>
+        <v>-2.0248</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6309</v>
+        <v>2.1084</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7354</v>
+        <v>-4.1332</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2544</v>
+        <v>-3.0574</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5359</v>
+        <v>-1.7878</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7185</v>
+        <v>-1.2696</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3589</v>
+        <v>1.1503</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1153</v>
+        <v>1.0463</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2436</v>
+        <v>0.104</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.6133</v>
+        <v>-4.2078</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.6512</v>
+        <v>-2.8341</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9621</v>
+        <v>-1.3737</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1402</v>
+        <v>-1.0733</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2719</v>
+        <v>-0.2658</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1317</v>
+        <v>-0.8075</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2821</v>
+        <v>0.9418</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>J. GIRALDO SISTIAGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6614</v>
+        <v>-2.363</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5263</v>
+        <v>-0.4096</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1877</v>
+        <v>-1.9534</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0574</v>
+        <v>-3.2544</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7878</v>
+        <v>-2.5359</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2696</v>
+        <v>-0.7185</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1503</v>
+        <v>0.3589</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0463</v>
+        <v>0.1153</v>
       </c>
       <c r="L8" t="n">
-        <v>0.104</v>
+        <v>0.2436</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.2078</v>
+        <v>-3.6133</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.8341</v>
+        <v>-2.6512</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3737</v>
+        <v>-0.9621</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7099</v>
+        <v>-1.137</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8479</v>
+        <v>-1.0507</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.862</v>
+        <v>-0.0863</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9418</v>
+        <v>0.2821</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.789</v>
+        <v>-3.2412</v>
       </c>
       <c r="E9" t="n">
-        <v>1.63</v>
+        <v>1.1506</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.419</v>
+        <v>-4.3918</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9672</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1994</v>
+        <v>-0.6516</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5473</v>
+        <v>0.0678</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7467</v>
+        <v>-0.7195</v>
       </c>
       <c r="V9" t="n">
         <v>0.3776</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2001</v>
+        <v>-4.2241</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8466</v>
+        <v>-0.6253</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3535</v>
+        <v>-3.5988</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3398</v>
@@ -1234,13 +1234,13 @@
         <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7826</v>
+        <v>-0.8067</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0296</v>
+        <v>-0.8084</v>
       </c>
       <c r="U10" t="n">
-        <v>0.247</v>
+        <v>0.0017</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4955</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7963</v>
+        <v>-4.9603</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0255</v>
+        <v>-3.3258</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7708</v>
+        <v>-1.6345</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9786</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4296</v>
+        <v>-0.5936</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.12</v>
+        <v>-0.4203</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3095</v>
+        <v>-0.1733</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6119</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.965</v>
+        <v>-5.7956</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5138</v>
+        <v>-1.3716</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.4513</v>
+        <v>-4.424</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9341</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0608</v>
+        <v>-0.8914</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1806</v>
+        <v>-0.0384</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8802</v>
+        <v>-0.8529</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.6729</v>
+        <v>-25.4615</v>
       </c>
       <c r="E13" t="n">
-        <v>5.179800000000001</v>
+        <v>6.391400000000003</v>
       </c>
       <c r="F13" t="n">
         <v>-31.8529</v>
@@ -1438,7 +1438,7 @@
         <v>-15.4476</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.031700000000001</v>
+        <v>-4.0317</v>
       </c>
       <c r="J13" t="n">
         <v>15.1164</v>
@@ -1468,13 +1468,13 @@
         <v>11.642</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.942600000000001</v>
+        <v>-8.7315</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.748200000000001</v>
+        <v>-4.5369</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.1943</v>
+        <v>-4.1944</v>
       </c>
       <c r="V13" t="n">
         <v>3.7195</v>
@@ -1483,13 +1483,13 @@
         <v>8.4239</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.7044</v>
+        <v>-4.704400000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1665</v>
+        <v>6.2542</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9261</v>
+        <v>6.9296</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2404</v>
+        <v>-0.6754</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3745</v>
+        <v>7.8908</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8892</v>
+        <v>1.3075</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4854</v>
+        <v>6.5833</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0063</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9536</v>
+        <v>2.7723</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0527</v>
+        <v>6.3331</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6317</v>
+        <v>-1.2146</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0645</v>
+        <v>-1.4649</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5673</v>
+        <v>0.2502</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5821</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9278</v>
+        <v>0.7694</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6079</v>
+        <v>0.1705</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3199</v>
+        <v>0.5989</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2821</v>
+        <v>-0.6597</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0173</v>
+        <v>5.6025</v>
       </c>
       <c r="E15" t="n">
-        <v>6.5292</v>
+        <v>4.5257</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5118</v>
+        <v>1.0769</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8908</v>
+        <v>3.3745</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3075</v>
+        <v>1.8892</v>
       </c>
       <c r="I15" t="n">
-        <v>6.5833</v>
+        <v>1.4854</v>
       </c>
       <c r="J15" t="n">
-        <v>9.105399999999999</v>
+        <v>5.0063</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7723</v>
+        <v>2.9536</v>
       </c>
       <c r="L15" t="n">
-        <v>6.3331</v>
+        <v>2.0527</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2146</v>
+        <v>-1.6317</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4649</v>
+        <v>-1.0645</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2502</v>
+        <v>-0.5673</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5325</v>
+        <v>1.3638</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2299</v>
+        <v>0.2075</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7625</v>
+        <v>1.1564</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6597</v>
+        <v>0.2821</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5642</v>
+        <v>0.2821</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>J. ABRIL RAMIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8262</v>
+        <v>5.6002</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5332</v>
+        <v>4.7697</v>
       </c>
       <c r="F16" t="n">
-        <v>0.293</v>
+        <v>0.8305</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0007</v>
+        <v>4.0811</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5145</v>
+        <v>3.6456</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5138</v>
+        <v>0.4354</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2703</v>
+        <v>5.4113</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3614</v>
+        <v>4.0081</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0911</v>
+        <v>1.4031</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2696</v>
+        <v>-1.3302</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8469</v>
+        <v>-0.3625</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4227</v>
+        <v>-0.9677</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4195</v>
+        <v>0.743</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6509</v>
+        <v>0.3286</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7685</v>
+        <v>0.4144</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ABRIL RAMIRO</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4996</v>
+        <v>3.7801</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9689</v>
+        <v>3.7324</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.0477</v>
       </c>
       <c r="G17" t="n">
-        <v>4.0811</v>
+        <v>1.0007</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6456</v>
+        <v>2.5145</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4354</v>
+        <v>-1.5138</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4113</v>
+        <v>2.2703</v>
       </c>
       <c r="K17" t="n">
-        <v>4.0081</v>
+        <v>3.3614</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4031</v>
+        <v>-1.0911</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3302</v>
+        <v>-1.2696</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3625</v>
+        <v>-0.8469</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9677</v>
+        <v>-0.4227</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3576</v>
+        <v>1.3734</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4722</v>
+        <v>0.8501</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1146</v>
+        <v>0.5232</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3857</v>
+        <v>3.6577</v>
       </c>
       <c r="E18" t="n">
-        <v>3.9017</v>
+        <v>3.201</v>
       </c>
       <c r="F18" t="n">
-        <v>0.484</v>
+        <v>0.4568</v>
       </c>
       <c r="G18" t="n">
         <v>1.5401</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4859</v>
+        <v>0.7579</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9107</v>
+        <v>0.21</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5752</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>1.5537</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.203</v>
+        <v>2.0939</v>
       </c>
       <c r="E19" t="n">
         <v>3.4354</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2324</v>
+        <v>-1.3415</v>
       </c>
       <c r="G19" t="n">
         <v>4.4286</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2968</v>
+        <v>1.1878</v>
       </c>
       <c r="T19" t="n">
         <v>0.4374</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.7504</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6119</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.228</v>
+        <v>2.0471</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9097</v>
+        <v>1.8106</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3183</v>
+        <v>0.2365</v>
       </c>
       <c r="G20" t="n">
         <v>1.7076</v>
@@ -2014,13 +2014,13 @@
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1025</v>
+        <v>0.9217</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6662</v>
+        <v>0.2347</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7687</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5595</v>
+        <v>1.1779</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8103</v>
+        <v>2.2107</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2508</v>
+        <v>-1.0328</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9540999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2912</v>
+        <v>0.9096</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1222</v>
+        <v>0.5226</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1689</v>
+        <v>0.387</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3299</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0607</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>3.4055</v>
+        <v>2.4045</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3448</v>
+        <v>-3.1268</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4378</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>2.3537</v>
+        <v>1.5708</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3788</v>
+        <v>1.3778</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0251</v>
+        <v>0.1929</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2134</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4023</v>
+        <v>-1.2476</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6661</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7361</v>
+        <v>-0.6816</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1565</v>
@@ -2248,13 +2248,13 @@
         <v>0.194</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1577</v>
+        <v>-0.0031</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0606</v>
+        <v>0.0395</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2821</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8712</v>
+        <v>-1.5709</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9009</v>
+        <v>-0.6006</v>
       </c>
       <c r="F24" t="n">
         <v>-0.9703000000000001</v>
@@ -2326,10 +2326,10 @@
         <v>0.5821</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0482</v>
+        <v>0.3485</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4845</v>
+        <v>-0.1842</v>
       </c>
       <c r="U24" t="n">
         <v>0.5328000000000001</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>26.67299999999999</v>
+        <v>26.6728</v>
       </c>
       <c r="E25" t="n">
-        <v>31.853</v>
+        <v>31.85299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.1798</v>
+        <v>-5.18</v>
       </c>
       <c r="G25" t="n">
         <v>19.4795</v>
@@ -2404,7 +2404,7 @@
         <v>12.6121</v>
       </c>
       <c r="S25" t="n">
-        <v>9.942799999999998</v>
+        <v>9.9428</v>
       </c>
       <c r="T25" t="n">
         <v>4.194500000000001</v>
